--- a/data/data_raw/eurostat/AT_electricity_fuel_type_nrg_cb_pem.xlsx
+++ b/data/data_raw/eurostat/AT_electricity_fuel_type_nrg_cb_pem.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HE46"/>
+  <dimension ref="A1:HK46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1489,6 +1489,36 @@
           <t>2025-04</t>
         </is>
       </c>
+      <c r="HF1" s="1" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="HG1" s="1" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="HH1" s="1" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="HI1" s="1" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="HJ1" s="1" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="HK1" s="1" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -2137,6 +2167,24 @@
       </c>
       <c r="HE2" t="n">
         <v>6135.493</v>
+      </c>
+      <c r="HF2" t="n">
+        <v>5981.09</v>
+      </c>
+      <c r="HG2" t="n">
+        <v>6273.29</v>
+      </c>
+      <c r="HH2" t="n">
+        <v>6576.128</v>
+      </c>
+      <c r="HI2" t="n">
+        <v>6408.995</v>
+      </c>
+      <c r="HJ2" t="n">
+        <v>5380.976</v>
+      </c>
+      <c r="HK2" t="n">
+        <v>5947.434</v>
       </c>
     </row>
     <row r="3">
@@ -2786,6 +2834,24 @@
       </c>
       <c r="HE3" t="n">
         <v>1177.516</v>
+      </c>
+      <c r="HF3" t="n">
+        <v>684.5549999999999</v>
+      </c>
+      <c r="HG3" t="n">
+        <v>650.721</v>
+      </c>
+      <c r="HH3" t="n">
+        <v>767.033</v>
+      </c>
+      <c r="HI3" t="n">
+        <v>682.1369999999999</v>
+      </c>
+      <c r="HJ3" t="n">
+        <v>768.861</v>
+      </c>
+      <c r="HK3" t="n">
+        <v>1522.94</v>
       </c>
     </row>
     <row r="4">
@@ -3243,6 +3309,24 @@
       </c>
       <c r="HE4" t="n">
         <v>19.192</v>
+      </c>
+      <c r="HF4" t="n">
+        <v>11.445</v>
+      </c>
+      <c r="HG4" t="n">
+        <v>10.373</v>
+      </c>
+      <c r="HH4" t="n">
+        <v>11.664</v>
+      </c>
+      <c r="HI4" t="n">
+        <v>10.643</v>
+      </c>
+      <c r="HJ4" t="n">
+        <v>14.289</v>
+      </c>
+      <c r="HK4" t="n">
+        <v>25.607</v>
       </c>
     </row>
     <row r="5">
@@ -3677,6 +3761,24 @@
       <c r="HE5" t="n">
         <v>368.236</v>
       </c>
+      <c r="HF5" t="n">
+        <v>349.651</v>
+      </c>
+      <c r="HG5" t="n">
+        <v>294.47</v>
+      </c>
+      <c r="HH5" t="n">
+        <v>340.296</v>
+      </c>
+      <c r="HI5" t="n">
+        <v>332.694</v>
+      </c>
+      <c r="HJ5" t="n">
+        <v>320.051</v>
+      </c>
+      <c r="HK5" t="n">
+        <v>375.643</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -4110,6 +4212,24 @@
       <c r="HE6" t="n">
         <v>6.002</v>
       </c>
+      <c r="HF6" t="n">
+        <v>5.846</v>
+      </c>
+      <c r="HG6" t="n">
+        <v>4.694</v>
+      </c>
+      <c r="HH6" t="n">
+        <v>5.175</v>
+      </c>
+      <c r="HI6" t="n">
+        <v>5.191</v>
+      </c>
+      <c r="HJ6" t="n">
+        <v>5.948</v>
+      </c>
+      <c r="HK6" t="n">
+        <v>6.316</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -4543,6 +4663,24 @@
       <c r="HE7" t="n">
         <v>67.973</v>
       </c>
+      <c r="HF7" t="n">
+        <v>59.01</v>
+      </c>
+      <c r="HG7" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="HH7" t="n">
+        <v>66.666</v>
+      </c>
+      <c r="HI7" t="n">
+        <v>60.741</v>
+      </c>
+      <c r="HJ7" t="n">
+        <v>41.491</v>
+      </c>
+      <c r="HK7" t="n">
+        <v>61.361</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -4976,6 +5114,24 @@
       <c r="HE8" t="n">
         <v>1.108</v>
       </c>
+      <c r="HF8" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="HG8" t="n">
+        <v>1.022</v>
+      </c>
+      <c r="HH8" t="n">
+        <v>1.014</v>
+      </c>
+      <c r="HI8" t="n">
+        <v>0.948</v>
+      </c>
+      <c r="HJ8" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="HK8" t="n">
+        <v>1.032</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -5409,6 +5565,24 @@
       <c r="HE9" t="n">
         <v>131.081</v>
       </c>
+      <c r="HF9" t="n">
+        <v>107.179</v>
+      </c>
+      <c r="HG9" t="n">
+        <v>127.732</v>
+      </c>
+      <c r="HH9" t="n">
+        <v>161.231</v>
+      </c>
+      <c r="HI9" t="n">
+        <v>158.564</v>
+      </c>
+      <c r="HJ9" t="n">
+        <v>147.54</v>
+      </c>
+      <c r="HK9" t="n">
+        <v>174.664</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -5842,6 +6016,24 @@
       <c r="HE10" t="n">
         <v>2.136</v>
       </c>
+      <c r="HF10" t="n">
+        <v>1.792</v>
+      </c>
+      <c r="HG10" t="n">
+        <v>2.036</v>
+      </c>
+      <c r="HH10" t="n">
+        <v>2.452</v>
+      </c>
+      <c r="HI10" t="n">
+        <v>2.474</v>
+      </c>
+      <c r="HJ10" t="n">
+        <v>2.742</v>
+      </c>
+      <c r="HK10" t="n">
+        <v>2.937</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -6275,6 +6467,24 @@
       <c r="HE11" t="n">
         <v>559.6319999999999</v>
       </c>
+      <c r="HF11" t="n">
+        <v>119.565</v>
+      </c>
+      <c r="HG11" t="n">
+        <v>116.322</v>
+      </c>
+      <c r="HH11" t="n">
+        <v>147.89</v>
+      </c>
+      <c r="HI11" t="n">
+        <v>88.94799999999999</v>
+      </c>
+      <c r="HJ11" t="n">
+        <v>213.097</v>
+      </c>
+      <c r="HK11" t="n">
+        <v>862.0839999999999</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -6708,6 +6918,24 @@
       <c r="HE12" t="n">
         <v>9.121</v>
       </c>
+      <c r="HF12" t="n">
+        <v>1.999</v>
+      </c>
+      <c r="HG12" t="n">
+        <v>1.854</v>
+      </c>
+      <c r="HH12" t="n">
+        <v>2.249</v>
+      </c>
+      <c r="HI12" t="n">
+        <v>1.388</v>
+      </c>
+      <c r="HJ12" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="HK12" t="n">
+        <v>14.495</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -7141,6 +7369,24 @@
       <c r="HE13" t="n">
         <v>50.594</v>
       </c>
+      <c r="HF13" t="n">
+        <v>49.15</v>
+      </c>
+      <c r="HG13" t="n">
+        <v>48.097</v>
+      </c>
+      <c r="HH13" t="n">
+        <v>50.95</v>
+      </c>
+      <c r="HI13" t="n">
+        <v>41.19</v>
+      </c>
+      <c r="HJ13" t="n">
+        <v>46.682</v>
+      </c>
+      <c r="HK13" t="n">
+        <v>49.188</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -7574,6 +7820,24 @@
       <c r="HE14" t="n">
         <v>0.825</v>
       </c>
+      <c r="HF14" t="n">
+        <v>0.822</v>
+      </c>
+      <c r="HG14" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="HH14" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="HI14" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="HJ14" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="HK14" t="n">
+        <v>0.827</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -8007,6 +8271,24 @@
       <c r="HE15" t="n">
         <v>5326.213</v>
       </c>
+      <c r="HF15" t="n">
+        <v>5646.186</v>
+      </c>
+      <c r="HG15" t="n">
+        <v>5917.039</v>
+      </c>
+      <c r="HH15" t="n">
+        <v>6149.391</v>
+      </c>
+      <c r="HI15" t="n">
+        <v>6059.552</v>
+      </c>
+      <c r="HJ15" t="n">
+        <v>4932.166</v>
+      </c>
+      <c r="HK15" t="n">
+        <v>4800.137</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -8440,6 +8722,24 @@
       <c r="HE16" t="n">
         <v>86.81</v>
       </c>
+      <c r="HF16" t="n">
+        <v>94.401</v>
+      </c>
+      <c r="HG16" t="n">
+        <v>94.321</v>
+      </c>
+      <c r="HH16" t="n">
+        <v>93.511</v>
+      </c>
+      <c r="HI16" t="n">
+        <v>94.548</v>
+      </c>
+      <c r="HJ16" t="n">
+        <v>91.65900000000001</v>
+      </c>
+      <c r="HK16" t="n">
+        <v>80.709</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -9088,6 +9388,24 @@
       </c>
       <c r="HE17" t="n">
         <v>2973.481</v>
+      </c>
+      <c r="HF17" t="n">
+        <v>3660.375</v>
+      </c>
+      <c r="HG17" t="n">
+        <v>3700.029</v>
+      </c>
+      <c r="HH17" t="n">
+        <v>3955.837</v>
+      </c>
+      <c r="HI17" t="n">
+        <v>3971.91</v>
+      </c>
+      <c r="HJ17" t="n">
+        <v>3178.284</v>
+      </c>
+      <c r="HK17" t="n">
+        <v>2783.83</v>
       </c>
     </row>
     <row r="18">
@@ -9545,6 +9863,24 @@
       </c>
       <c r="HE18" t="n">
         <v>48.464</v>
+      </c>
+      <c r="HF18" t="n">
+        <v>61.199</v>
+      </c>
+      <c r="HG18" t="n">
+        <v>58.981</v>
+      </c>
+      <c r="HH18" t="n">
+        <v>60.155</v>
+      </c>
+      <c r="HI18" t="n">
+        <v>61.974</v>
+      </c>
+      <c r="HJ18" t="n">
+        <v>59.065</v>
+      </c>
+      <c r="HK18" t="n">
+        <v>46.807</v>
       </c>
     </row>
     <row r="19">
@@ -9979,6 +10315,24 @@
       <c r="HE19" t="n">
         <v>2060.616</v>
       </c>
+      <c r="HF19" t="n">
+        <v>2518.407</v>
+      </c>
+      <c r="HG19" t="n">
+        <v>2521.416</v>
+      </c>
+      <c r="HH19" t="n">
+        <v>2766.253</v>
+      </c>
+      <c r="HI19" t="n">
+        <v>2586.905</v>
+      </c>
+      <c r="HJ19" t="n">
+        <v>2095.295</v>
+      </c>
+      <c r="HK19" t="n">
+        <v>1895.262</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -10412,6 +10766,24 @@
       <c r="HE20" t="n">
         <v>33.585</v>
       </c>
+      <c r="HF20" t="n">
+        <v>42.106</v>
+      </c>
+      <c r="HG20" t="n">
+        <v>40.193</v>
+      </c>
+      <c r="HH20" t="n">
+        <v>42.065</v>
+      </c>
+      <c r="HI20" t="n">
+        <v>40.364</v>
+      </c>
+      <c r="HJ20" t="n">
+        <v>38.939</v>
+      </c>
+      <c r="HK20" t="n">
+        <v>31.867</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -10845,6 +11217,24 @@
       <c r="HE21" t="n">
         <v>912.865</v>
       </c>
+      <c r="HF21" t="n">
+        <v>1141.968</v>
+      </c>
+      <c r="HG21" t="n">
+        <v>1178.613</v>
+      </c>
+      <c r="HH21" t="n">
+        <v>1189.584</v>
+      </c>
+      <c r="HI21" t="n">
+        <v>1385.005</v>
+      </c>
+      <c r="HJ21" t="n">
+        <v>1082.989</v>
+      </c>
+      <c r="HK21" t="n">
+        <v>888.568</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -11278,6 +11668,24 @@
       <c r="HE22" t="n">
         <v>14.878</v>
       </c>
+      <c r="HF22" t="n">
+        <v>19.093</v>
+      </c>
+      <c r="HG22" t="n">
+        <v>18.788</v>
+      </c>
+      <c r="HH22" t="n">
+        <v>18.089</v>
+      </c>
+      <c r="HI22" t="n">
+        <v>21.61</v>
+      </c>
+      <c r="HJ22" t="n">
+        <v>20.126</v>
+      </c>
+      <c r="HK22" t="n">
+        <v>14.94</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -11711,6 +12119,24 @@
       <c r="HE23" t="n">
         <v>0</v>
       </c>
+      <c r="HF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -12112,6 +12538,12 @@
       <c r="HC24" t="inlineStr"/>
       <c r="HD24" t="inlineStr"/>
       <c r="HE24" t="inlineStr"/>
+      <c r="HF24" t="inlineStr"/>
+      <c r="HG24" t="inlineStr"/>
+      <c r="HH24" t="inlineStr"/>
+      <c r="HI24" t="inlineStr"/>
+      <c r="HJ24" t="inlineStr"/>
+      <c r="HK24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -12759,6 +13191,24 @@
         <v>0</v>
       </c>
       <c r="HE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="HF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13218,6 +13668,24 @@
       <c r="HE26" t="n">
         <v>0</v>
       </c>
+      <c r="HF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -13866,6 +14334,24 @@
       </c>
       <c r="HE27" t="n">
         <v>920.353</v>
+      </c>
+      <c r="HF27" t="n">
+        <v>566.486</v>
+      </c>
+      <c r="HG27" t="n">
+        <v>573.997</v>
+      </c>
+      <c r="HH27" t="n">
+        <v>750.348</v>
+      </c>
+      <c r="HI27" t="n">
+        <v>533.361</v>
+      </c>
+      <c r="HJ27" t="n">
+        <v>568.957</v>
+      </c>
+      <c r="HK27" t="n">
+        <v>1001.569</v>
       </c>
     </row>
     <row r="28">
@@ -14323,6 +14809,24 @@
       </c>
       <c r="HE28" t="n">
         <v>15</v>
+      </c>
+      <c r="HF28" t="n">
+        <v>9.471</v>
+      </c>
+      <c r="HG28" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="HH28" t="n">
+        <v>11.41</v>
+      </c>
+      <c r="HI28" t="n">
+        <v>8.321999999999999</v>
+      </c>
+      <c r="HJ28" t="n">
+        <v>10.573</v>
+      </c>
+      <c r="HK28" t="n">
+        <v>16.84</v>
       </c>
     </row>
     <row r="29">
@@ -14757,6 +15261,24 @@
       <c r="HE29" t="n">
         <v>920.353</v>
       </c>
+      <c r="HF29" t="n">
+        <v>566.486</v>
+      </c>
+      <c r="HG29" t="n">
+        <v>573.997</v>
+      </c>
+      <c r="HH29" t="n">
+        <v>750.348</v>
+      </c>
+      <c r="HI29" t="n">
+        <v>533.361</v>
+      </c>
+      <c r="HJ29" t="n">
+        <v>568.957</v>
+      </c>
+      <c r="HK29" t="n">
+        <v>1001.569</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -15190,6 +15712,24 @@
       <c r="HE30" t="n">
         <v>15</v>
       </c>
+      <c r="HF30" t="n">
+        <v>9.471</v>
+      </c>
+      <c r="HG30" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="HH30" t="n">
+        <v>11.41</v>
+      </c>
+      <c r="HI30" t="n">
+        <v>8.321999999999999</v>
+      </c>
+      <c r="HJ30" t="n">
+        <v>10.573</v>
+      </c>
+      <c r="HK30" t="n">
+        <v>16.84</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -15623,6 +16163,24 @@
       <c r="HE31" t="n">
         <v>0</v>
       </c>
+      <c r="HF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -16056,6 +16614,24 @@
       <c r="HE32" t="n">
         <v>0</v>
       </c>
+      <c r="HF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -16489,6 +17065,24 @@
       <c r="HE33" t="n">
         <v>1064.143</v>
       </c>
+      <c r="HF33" t="n">
+        <v>1069.674</v>
+      </c>
+      <c r="HG33" t="n">
+        <v>1348.543</v>
+      </c>
+      <c r="HH33" t="n">
+        <v>1102.91</v>
+      </c>
+      <c r="HI33" t="n">
+        <v>1221.587</v>
+      </c>
+      <c r="HJ33" t="n">
+        <v>864.874</v>
+      </c>
+      <c r="HK33" t="n">
+        <v>639.095</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -16922,6 +17516,24 @@
       <c r="HE34" t="n">
         <v>17.344</v>
       </c>
+      <c r="HF34" t="n">
+        <v>17.884</v>
+      </c>
+      <c r="HG34" t="n">
+        <v>21.497</v>
+      </c>
+      <c r="HH34" t="n">
+        <v>16.771</v>
+      </c>
+      <c r="HI34" t="n">
+        <v>19.061</v>
+      </c>
+      <c r="HJ34" t="n">
+        <v>16.073</v>
+      </c>
+      <c r="HK34" t="n">
+        <v>10.746</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -17355,6 +17967,24 @@
       <c r="HE35" t="n">
         <v>0</v>
       </c>
+      <c r="HF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -17788,6 +18418,24 @@
       <c r="HE36" t="n">
         <v>0</v>
       </c>
+      <c r="HF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -18221,6 +18869,24 @@
       <c r="HE37" t="n">
         <v>1064.143</v>
       </c>
+      <c r="HF37" t="n">
+        <v>1069.674</v>
+      </c>
+      <c r="HG37" t="n">
+        <v>1348.543</v>
+      </c>
+      <c r="HH37" t="n">
+        <v>1102.91</v>
+      </c>
+      <c r="HI37" t="n">
+        <v>1221.587</v>
+      </c>
+      <c r="HJ37" t="n">
+        <v>864.874</v>
+      </c>
+      <c r="HK37" t="n">
+        <v>639.095</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -18654,6 +19320,24 @@
       <c r="HE38" t="n">
         <v>17.344</v>
       </c>
+      <c r="HF38" t="n">
+        <v>17.884</v>
+      </c>
+      <c r="HG38" t="n">
+        <v>21.497</v>
+      </c>
+      <c r="HH38" t="n">
+        <v>16.771</v>
+      </c>
+      <c r="HI38" t="n">
+        <v>19.061</v>
+      </c>
+      <c r="HJ38" t="n">
+        <v>16.073</v>
+      </c>
+      <c r="HK38" t="n">
+        <v>10.746</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -19087,6 +19771,24 @@
       <c r="HE39" t="n">
         <v>0</v>
       </c>
+      <c r="HF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -19520,6 +20222,24 @@
       <c r="HE40" t="n">
         <v>0</v>
       </c>
+      <c r="HF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -20167,6 +20887,24 @@
         <v>0</v>
       </c>
       <c r="HE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="HF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -20624,6 +21362,24 @@
         <v>0</v>
       </c>
       <c r="HE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="HF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK42" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21059,6 +21815,24 @@
       <c r="HE43" t="n">
         <v>0</v>
       </c>
+      <c r="HF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI43" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -21490,6 +22264,24 @@
         <v>0</v>
       </c>
       <c r="HE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="HF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI44" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21757,6 +22549,24 @@
       <c r="HE45" t="n">
         <v>809.28</v>
       </c>
+      <c r="HF45" t="n">
+        <v>334.904</v>
+      </c>
+      <c r="HG45" t="n">
+        <v>356.251</v>
+      </c>
+      <c r="HH45" t="n">
+        <v>426.737</v>
+      </c>
+      <c r="HI45" t="n">
+        <v>349.443</v>
+      </c>
+      <c r="HJ45" t="n">
+        <v>448.81</v>
+      </c>
+      <c r="HK45" t="n">
+        <v>1147.297</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -22022,6 +22832,24 @@
       <c r="HE46" t="n">
         <v>13.19</v>
       </c>
+      <c r="HF46" t="n">
+        <v>5.599</v>
+      </c>
+      <c r="HG46" t="n">
+        <v>5.679</v>
+      </c>
+      <c r="HH46" t="n">
+        <v>6.489</v>
+      </c>
+      <c r="HI46" t="n">
+        <v>5.452</v>
+      </c>
+      <c r="HJ46" t="n">
+        <v>8.340999999999999</v>
+      </c>
+      <c r="HK46" t="n">
+        <v>19.291</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
